--- a/_posts/2023-02-12-ipipneo300fr/ipipneo_300fr.xlsx
+++ b/_posts/2023-02-12-ipipneo300fr/ipipneo_300fr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ouriagan\Documents\ipipneoadaptationfr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ouriagan\Documents\blog\_posts\2023-02-12-ipipneo300fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157A1E3E-8E1D-41EF-B2F6-C0F4033D5235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AA1495-C57A-4255-947F-6C599FB5789E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{AB162525-3802-41D8-93AF-7BC18205CD06}"/>
   </bookViews>
@@ -938,10 +938,10 @@
     <t>Je fais souvent des plans de dernière minute.</t>
   </si>
   <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>question</t>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Question</t>
   </si>
 </sst>
 </file>
@@ -3714,15 +3714,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F00809B49A725046A477075F23A5E080" ma:contentTypeVersion="12" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="f09ab1eed3b4290083c17e12e42e6a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="39f91322-7f72-41af-8a27-d7257590466c" xmlns:ns4="b3801da7-c30a-448d-86c3-45b2a9822e84" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9569f3819539905949c81958a61cacc8" ns3:_="" ns4:_="">
     <xsd:import namespace="39f91322-7f72-41af-8a27-d7257590466c"/>
@@ -3939,6 +3930,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3946,14 +3946,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9CF6906-387F-488D-B47E-692669453EEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1AFF935-F51D-42C1-B0DE-E92A06502EC1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3968,6 +3960,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9CF6906-387F-488D-B47E-692669453EEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
